--- a/Team-Data/2007-08/12-25-2007-08.xlsx
+++ b/Team-Data/2007-08/12-25-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -772,7 +839,7 @@
         <v>29</v>
       </c>
       <c r="AO2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP2" t="n">
         <v>6</v>
@@ -784,7 +851,7 @@
         <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT2" t="n">
         <v>24</v>
@@ -805,10 +872,10 @@
         <v>19</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
         <v>23</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -960,7 +1027,7 @@
         <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR3" t="n">
         <v>29</v>
@@ -987,7 +1054,7 @@
         <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
         <v>7</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1188,7 @@
         <v>27</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK4" t="n">
         <v>21</v>
@@ -1145,13 +1212,13 @@
         <v>30</v>
       </c>
       <c r="AR4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS4" t="n">
         <v>30</v>
       </c>
       <c r="AT4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU4" t="n">
         <v>24</v>
@@ -1160,7 +1227,7 @@
         <v>27</v>
       </c>
       <c r="AW4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX4" t="n">
         <v>16</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1370,7 @@
         <v>25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1318,7 +1385,7 @@
         <v>28</v>
       </c>
       <c r="AO5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP5" t="n">
         <v>25</v>
@@ -1336,10 +1403,10 @@
         <v>7</v>
       </c>
       <c r="AU5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW5" t="n">
         <v>13</v>
@@ -1351,7 +1418,7 @@
         <v>29</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA5" t="n">
         <v>19</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
         <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>0.448</v>
+        <v>0.429</v>
       </c>
       <c r="H6" t="n">
         <v>48.7</v>
@@ -1407,28 +1474,28 @@
         <v>35.7</v>
       </c>
       <c r="J6" t="n">
-        <v>81.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0.436</v>
       </c>
       <c r="L6" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M6" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="N6" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O6" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P6" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.719</v>
+        <v>0.72</v>
       </c>
       <c r="R6" t="n">
         <v>12.4</v>
@@ -1440,49 +1507,49 @@
         <v>43</v>
       </c>
       <c r="U6" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="V6" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W6" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="AB6" t="n">
         <v>96.40000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>-3.9</v>
+        <v>-4.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AF6" t="n">
         <v>22</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH6" t="n">
         <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ6" t="n">
         <v>13</v>
@@ -1497,7 +1564,7 @@
         <v>12</v>
       </c>
       <c r="AN6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="n">
         <v>19</v>
@@ -1509,7 +1576,7 @@
         <v>24</v>
       </c>
       <c r="AR6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
         <v>16</v>
@@ -1524,25 +1591,25 @@
         <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ6" t="n">
         <v>24</v>
       </c>
       <c r="BA6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB6" t="n">
         <v>17</v>
       </c>
       <c r="BC6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -1649,19 +1716,19 @@
         <v>3.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
         <v>3</v>
       </c>
       <c r="AF7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
         <v>12</v>
@@ -1676,7 +1743,7 @@
         <v>18</v>
       </c>
       <c r="AM7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN7" t="n">
         <v>15</v>
@@ -1709,7 +1776,7 @@
         <v>28</v>
       </c>
       <c r="AX7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY7" t="n">
         <v>5</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1846,7 +1913,7 @@
         <v>9</v>
       </c>
       <c r="AI8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ8" t="n">
         <v>6</v>
@@ -1861,7 +1928,7 @@
         <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1903,7 +1970,7 @@
         <v>1</v>
       </c>
       <c r="BB8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC8" t="n">
         <v>8</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>9.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2034,7 +2101,7 @@
         <v>20</v>
       </c>
       <c r="AK9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL9" t="n">
         <v>20</v>
@@ -2085,7 +2152,7 @@
         <v>21</v>
       </c>
       <c r="BB9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>1.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
         <v>9</v>
@@ -2207,7 +2274,7 @@
         <v>10</v>
       </c>
       <c r="AH10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>0.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>16</v>
@@ -2389,13 +2456,13 @@
         <v>17</v>
       </c>
       <c r="AH11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
         <v>19</v>
       </c>
       <c r="AJ11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK11" t="n">
         <v>26</v>
@@ -2404,7 +2471,7 @@
         <v>12</v>
       </c>
       <c r="AM11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN11" t="n">
         <v>25</v>
@@ -2425,7 +2492,7 @@
         <v>9</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
         <v>17</v>
@@ -2449,7 +2516,7 @@
         <v>24</v>
       </c>
       <c r="BB11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC11" t="n">
         <v>14</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>0.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF12" t="n">
         <v>13</v>
@@ -2571,7 +2638,7 @@
         <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2595,7 +2662,7 @@
         <v>17</v>
       </c>
       <c r="AP12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ12" t="n">
         <v>16</v>
@@ -2616,7 +2683,7 @@
         <v>16</v>
       </c>
       <c r="AW12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2838,7 @@
         <v>25</v>
       </c>
       <c r="AN13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO13" t="n">
         <v>8</v>
@@ -2780,13 +2847,13 @@
         <v>11</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR13" t="n">
         <v>22</v>
       </c>
       <c r="AS13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
         <v>14</v>
@@ -2804,13 +2871,13 @@
         <v>8</v>
       </c>
       <c r="AY13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB13" t="n">
         <v>27</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -2845,64 +2912,64 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>0.643</v>
+        <v>0.63</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="J14" t="n">
-        <v>82.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.47</v>
+        <v>0.468</v>
       </c>
       <c r="L14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="N14" t="n">
-        <v>0.345</v>
+        <v>0.348</v>
       </c>
       <c r="O14" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="P14" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.767</v>
+        <v>0.763</v>
       </c>
       <c r="R14" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S14" t="n">
         <v>33.9</v>
       </c>
       <c r="T14" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
       <c r="U14" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V14" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W14" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X14" t="n">
         <v>4.9</v>
@@ -2911,22 +2978,22 @@
         <v>4.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="AA14" t="n">
         <v>23.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.4</v>
+        <v>105.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2938,25 +3005,25 @@
         <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL14" t="n">
         <v>10</v>
       </c>
       <c r="AM14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AN14" t="n">
         <v>18</v>
       </c>
       <c r="AO14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AP14" t="n">
         <v>4</v>
@@ -2986,19 +3053,19 @@
         <v>15</v>
       </c>
       <c r="AY14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA14" t="n">
         <v>6</v>
       </c>
       <c r="BB14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-3.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3126,7 +3193,7 @@
         <v>18</v>
       </c>
       <c r="AK15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL15" t="n">
         <v>6</v>
@@ -3165,7 +3232,7 @@
         <v>29</v>
       </c>
       <c r="AX15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY15" t="n">
         <v>14</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -3209,100 +3276,100 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E16" t="n">
         <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.286</v>
+        <v>0.296</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="J16" t="n">
-        <v>76.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="M16" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.335</v>
+        <v>0.34</v>
       </c>
       <c r="O16" t="n">
         <v>19.3</v>
       </c>
       <c r="P16" t="n">
-        <v>27.4</v>
+        <v>27.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.702</v>
+        <v>0.709</v>
       </c>
       <c r="R16" t="n">
         <v>9.6</v>
       </c>
       <c r="S16" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T16" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="U16" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V16" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W16" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X16" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>94.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>-4.4</v>
+        <v>-4.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE16" t="n">
         <v>26</v>
       </c>
       <c r="AF16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AH16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AI16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ16" t="n">
         <v>28</v>
@@ -3314,10 +3381,10 @@
         <v>27</v>
       </c>
       <c r="AM16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AN16" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>15</v>
@@ -3326,7 +3393,7 @@
         <v>10</v>
       </c>
       <c r="AQ16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR16" t="n">
         <v>27</v>
@@ -3335,16 +3402,16 @@
         <v>19</v>
       </c>
       <c r="AT16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU16" t="n">
         <v>25</v>
       </c>
       <c r="AV16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX16" t="n">
         <v>4</v>
@@ -3353,16 +3420,16 @@
         <v>1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3566,7 @@
         <v>23</v>
       </c>
       <c r="AN17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO17" t="n">
         <v>23</v>
@@ -3514,13 +3581,13 @@
         <v>10</v>
       </c>
       <c r="AS17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT17" t="n">
         <v>21</v>
       </c>
       <c r="AU17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV17" t="n">
         <v>19</v>
@@ -3532,16 +3599,16 @@
         <v>18</v>
       </c>
       <c r="AY17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ17" t="n">
         <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC17" t="n">
         <v>23</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3739,7 @@
         <v>7</v>
       </c>
       <c r="AK18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL18" t="n">
         <v>19</v>
@@ -3693,7 +3760,7 @@
         <v>23</v>
       </c>
       <c r="AR18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
         <v>23</v>
@@ -3708,7 +3775,7 @@
         <v>26</v>
       </c>
       <c r="AW18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX18" t="n">
         <v>22</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -3833,16 +3900,16 @@
         <v>-5</v>
       </c>
       <c r="AD19" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF19" t="n">
         <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH19" t="n">
         <v>4</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -4015,16 +4082,16 @@
         <v>2.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF20" t="n">
         <v>6</v>
       </c>
       <c r="AG20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH20" t="n">
         <v>4</v>
@@ -4042,7 +4109,7 @@
         <v>9</v>
       </c>
       <c r="AM20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN20" t="n">
         <v>7</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-7.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4230,7 +4297,7 @@
         <v>27</v>
       </c>
       <c r="AO21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP21" t="n">
         <v>9</v>
@@ -4242,7 +4309,7 @@
         <v>2</v>
       </c>
       <c r="AS21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT21" t="n">
         <v>12</v>
@@ -4251,7 +4318,7 @@
         <v>30</v>
       </c>
       <c r="AV21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW21" t="n">
         <v>22</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4485,7 @@
         <v>2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR22" t="n">
         <v>28</v>
@@ -4445,7 +4512,7 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE23" t="n">
         <v>20</v>
@@ -4576,7 +4643,7 @@
         <v>9</v>
       </c>
       <c r="AI23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ23" t="n">
         <v>19</v>
@@ -4621,10 +4688,10 @@
         <v>11</v>
       </c>
       <c r="AX23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ23" t="n">
         <v>9</v>
@@ -4636,7 +4703,7 @@
         <v>25</v>
       </c>
       <c r="BC23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E24" t="n">
         <v>19</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>0.679</v>
+        <v>0.704</v>
       </c>
       <c r="H24" t="n">
         <v>48</v>
@@ -4683,46 +4750,46 @@
         <v>42.2</v>
       </c>
       <c r="J24" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.493</v>
+        <v>0.494</v>
       </c>
       <c r="L24" t="n">
         <v>8.4</v>
       </c>
       <c r="M24" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0.372</v>
+        <v>0.37</v>
       </c>
       <c r="O24" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="P24" t="n">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.779</v>
+        <v>0.786</v>
       </c>
       <c r="R24" t="n">
         <v>8.6</v>
       </c>
       <c r="S24" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T24" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="U24" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="V24" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="W24" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X24" t="n">
         <v>6.4</v>
@@ -4731,19 +4798,19 @@
         <v>3.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>109.7</v>
+        <v>109.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4776,19 +4843,19 @@
         <v>6</v>
       </c>
       <c r="AO24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP24" t="n">
         <v>26</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AR24" t="n">
         <v>30</v>
       </c>
       <c r="AS24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT24" t="n">
         <v>26</v>
@@ -4800,7 +4867,7 @@
         <v>6</v>
       </c>
       <c r="AW24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX24" t="n">
         <v>2</v>
@@ -4818,7 +4885,7 @@
         <v>1</v>
       </c>
       <c r="BC24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
         <v>12</v>
       </c>
       <c r="G25" t="n">
-        <v>0.571</v>
+        <v>0.556</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4865,49 +4932,49 @@
         <v>35.9</v>
       </c>
       <c r="J25" t="n">
-        <v>77.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.461</v>
+        <v>0.465</v>
       </c>
       <c r="L25" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M25" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N25" t="n">
         <v>0.378</v>
       </c>
       <c r="O25" t="n">
-        <v>17.3</v>
+        <v>17.6</v>
       </c>
       <c r="P25" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="Q25" t="n">
         <v>0.75</v>
       </c>
       <c r="R25" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="T25" t="n">
-        <v>39.5</v>
+        <v>39</v>
       </c>
       <c r="U25" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="V25" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="W25" t="n">
         <v>5.6</v>
       </c>
       <c r="X25" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Y25" t="n">
         <v>3.6</v>
@@ -4916,25 +4983,25 @@
         <v>20</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.3</v>
+        <v>95.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>-1</v>
+        <v>-1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF25" t="n">
         <v>10</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
         <v>20</v>
@@ -4943,16 +5010,16 @@
         <v>18</v>
       </c>
       <c r="AJ25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AL25" t="n">
         <v>15</v>
       </c>
       <c r="AM25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN25" t="n">
         <v>4</v>
@@ -4967,16 +5034,16 @@
         <v>17</v>
       </c>
       <c r="AR25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AS25" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AT25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AU25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AV25" t="n">
         <v>9</v>
@@ -4985,7 +5052,7 @@
         <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY25" t="n">
         <v>3</v>
@@ -4994,13 +5061,13 @@
         <v>5</v>
       </c>
       <c r="BA25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC25" t="n">
         <v>18</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>17</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5189,7 @@
         <v>7</v>
       </c>
       <c r="AI26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ26" t="n">
         <v>23</v>
@@ -5140,7 +5207,7 @@
         <v>8</v>
       </c>
       <c r="AO26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP26" t="n">
         <v>7</v>
@@ -5149,13 +5216,13 @@
         <v>4</v>
       </c>
       <c r="AR26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS26" t="n">
         <v>28</v>
       </c>
       <c r="AT26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AU26" t="n">
         <v>29</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5377,7 @@
         <v>17</v>
       </c>
       <c r="AK27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL27" t="n">
         <v>4</v>
@@ -5331,7 +5398,7 @@
         <v>11</v>
       </c>
       <c r="AR27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS27" t="n">
         <v>11</v>
@@ -5358,7 +5425,7 @@
         <v>2</v>
       </c>
       <c r="BA27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB27" t="n">
         <v>12</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E28" t="n">
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G28" t="n">
-        <v>0.286</v>
+        <v>0.296</v>
       </c>
       <c r="H28" t="n">
         <v>48.4</v>
       </c>
       <c r="I28" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="J28" t="n">
-        <v>84.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L28" t="n">
         <v>4.7</v>
@@ -5423,103 +5490,103 @@
         <v>13.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="O28" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="P28" t="n">
-        <v>24.6</v>
+        <v>24.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.774</v>
+        <v>0.776</v>
       </c>
       <c r="R28" t="n">
         <v>11.6</v>
       </c>
       <c r="S28" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="T28" t="n">
-        <v>44.7</v>
+        <v>44.5</v>
       </c>
       <c r="U28" t="n">
         <v>20.6</v>
       </c>
       <c r="V28" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="W28" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="AA28" t="n">
         <v>21</v>
       </c>
       <c r="AB28" t="n">
-        <v>98.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC28" t="n">
-        <v>-7</v>
+        <v>-6.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE28" t="n">
         <v>26</v>
       </c>
       <c r="AF28" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG28" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AH28" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AI28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL28" t="n">
         <v>26</v>
       </c>
       <c r="AM28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AN28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR28" t="n">
         <v>16</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>15</v>
       </c>
       <c r="AS28" t="n">
         <v>3</v>
       </c>
       <c r="AT28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU28" t="n">
         <v>19</v>
@@ -5528,22 +5595,22 @@
         <v>30</v>
       </c>
       <c r="AW28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AY28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA28" t="n">
         <v>20</v>
       </c>
       <c r="BB28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC28" t="n">
         <v>28</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5723,7 @@
         <v>1</v>
       </c>
       <c r="AE29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF29" t="n">
         <v>15</v>
@@ -5668,7 +5735,7 @@
         <v>23</v>
       </c>
       <c r="AI29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF30" t="n">
         <v>15</v>
@@ -5868,7 +5935,7 @@
         <v>20</v>
       </c>
       <c r="AO30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP30" t="n">
         <v>2</v>
@@ -5910,7 +5977,7 @@
         <v>5</v>
       </c>
       <c r="BC30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
@@ -6047,19 +6114,19 @@
         <v>13</v>
       </c>
       <c r="AN31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO31" t="n">
         <v>13</v>
       </c>
       <c r="AP31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS31" t="n">
         <v>11</v>
@@ -6077,7 +6144,7 @@
         <v>17</v>
       </c>
       <c r="AX31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY31" t="n">
         <v>8</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-25-2007-08</t>
+          <t>2007-12-25</t>
         </is>
       </c>
     </row>
